--- a/docs/handoff/三场景核心实验训练配置.xlsx
+++ b/docs/handoff/三场景核心实验训练配置.xlsx
@@ -6226,7 +6226,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3d27c7bf276d709dd72dbf7cfdcbdb0cbfa281949a644d81d9cf730f17c29623</t>
+          <t>be41ce04dec8e70a31f2acedec1083f1134b1efb6797fd1aaa9fe4d11d3d0f02</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
